--- a/artfynd/A 37004-2025 artfynd.xlsx
+++ b/artfynd/A 37004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,6 +1120,361 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132841532</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6675</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100763</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Cinnoberbagge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cucujus cinnaberinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brunnby, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>657062</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6638673</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132841203</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brunnby, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>657038</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6638605</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132841554</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brunnby, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>657053</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6638647</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tät matta av blommande blåsippa</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37004-2025 artfynd.xlsx
+++ b/artfynd/A 37004-2025 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>132841554</v>
       </c>
       <c r="B8" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37004-2025 artfynd.xlsx
+++ b/artfynd/A 37004-2025 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>132841554</v>
       </c>
       <c r="B8" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37004-2025 artfynd.xlsx
+++ b/artfynd/A 37004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,71 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78348109</v>
+        <v>71753016</v>
       </c>
       <c r="B2" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>408</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Riddarsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Consolida regalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vedyxatippen, Upl</t>
+          <t>Vedyxatippen, nya delen i öster, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656455.9039473516</v>
+        <v>656507</v>
       </c>
       <c r="R2" t="n">
-        <v>6638667.826281511</v>
+        <v>6638646</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -766,22 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,73 +776,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nike Nylander</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nike Nylander</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131498839</v>
+        <v>102870398</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>101295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>408</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Riddarsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Consolida regalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vedyxne, Upl</t>
+          <t>Vedyxa östligaste, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656617</v>
+        <v>656351</v>
       </c>
       <c r="R3" t="n">
-        <v>6638920</v>
+        <v>6638356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,12 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +898,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Håkan Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Håkan Andersson, Camilla Andersson, Marcus Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498814</v>
+        <v>71663954</v>
       </c>
       <c r="B4" t="n">
-        <v>58635</v>
+        <v>106498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,38 +921,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>219848</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Buglossoides arvensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) I. M. Johnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vedyxne, Upl</t>
+          <t>Vedyxatippen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656772</v>
+        <v>656507</v>
       </c>
       <c r="R4" t="n">
-        <v>6638848</v>
+        <v>6638646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,12 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Grov skattning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,65 +1007,73 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498821</v>
+        <v>72978510</v>
       </c>
       <c r="B5" t="n">
-        <v>56483</v>
+        <v>107465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>1433</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Kranssalvia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Salvia verticillata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedyxne, Upl</t>
+          <t>Vedyxatippen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656786</v>
+        <v>656421</v>
       </c>
       <c r="R5" t="n">
-        <v>6638741</v>
+        <v>6638442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,12 +1100,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,91 +1124,74 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Owe Rosengren, Åke Berg, Rasmus Elleby, Hans Elleby, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132841532</v>
+        <v>71664869</v>
       </c>
       <c r="B6" t="n">
-        <v>6675</v>
+        <v>104787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100763</v>
+        <v>1708</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Sanddådra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Camelina microcarpa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Andrz. ex DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brunnby, Upl</t>
+          <t>Vedyxatippen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>657062</v>
+        <v>656507</v>
       </c>
       <c r="R6" t="n">
-        <v>6638673</v>
+        <v>6638646</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,12 +1215,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Nya området i NO</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,49 +1234,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132841203</v>
+        <v>131498848</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,45 +1263,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brunnby, Upl</t>
+          <t>Motaggsvamp, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>657038</v>
+        <v>656749</v>
       </c>
       <c r="R7" t="n">
-        <v>6638605</v>
+        <v>6638788</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,12 +1320,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,70 +1334,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132841554</v>
+        <v>131498854</v>
       </c>
       <c r="B8" t="n">
-        <v>101340</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brunnby, Upl</t>
+          <t>Vedyxne, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>657053</v>
+        <v>656680</v>
       </c>
       <c r="R8" t="n">
-        <v>6638647</v>
+        <v>6638857</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,17 +1421,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tät matta av blommande blåsippa</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,15 +1442,1236 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131499431</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vedyxne, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>656688</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6638833</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132841203</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brunnby, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>657038</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6638605</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132841532</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6826</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100763</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cinnoberbagge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cucujus cinnaberinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brunnby, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>657062</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6638673</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131498814</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vedyxne, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>656772</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6638848</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131498839</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vedyxne, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>656617</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6638920</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131498821</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vedyxne, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>656786</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6638741</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>78348109</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vedyxatippen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>656456</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6638668</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-05-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-05-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>57188</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>larv</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vedyxatippen NÖ, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>656444</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6638619</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2010-07-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2010-07-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Artbestämning med DNA-analys (Palo  Merilä, 2003)</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gunnar Carlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gunnar Carlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SLU, FOMA, metamorfosförändringar hos grodyngel</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>78798748</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106498</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219848</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sminkrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Buglossoides arvensis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) I. M. Johnst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vedyxatippen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>656414</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6638440</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-07-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-07-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>86617275</v>
+      </c>
+      <c r="B18" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brunnby, busshållplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>657060</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6638714</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-06-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Samuel Johnson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Samuel Johnson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132841554</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brunnby, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>657053</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6638647</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tät matta av blommande blåsippa</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
